--- a/project/outputs_xlsx_solution/test_new4.4-wide-NF-1.xlsx
+++ b/project/outputs_xlsx_solution/test_new4.4-wide-NF-1.xlsx
@@ -666,12 +666,6 @@
       <c r="BA1">
         <v>50</v>
       </c>
-      <c r="BB1">
-        <v>51</v>
-      </c>
-      <c r="BC1">
-        <v>52</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -953,12 +947,9 @@
         <v>6</v>
       </c>
       <c r="P12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" t="s">
         <v>10</v>
       </c>
       <c r="T12" t="s">
@@ -1008,12 +999,9 @@
         <v>6</v>
       </c>
       <c r="R14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="S14" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" t="s">
         <v>10</v>
       </c>
       <c r="U14" t="s">
@@ -1037,10 +1025,10 @@
         <v>6</v>
       </c>
       <c r="S15" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="T15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U15" t="s">
         <v>11</v>
@@ -1056,11 +1044,14 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
+      <c r="T16" t="s">
+        <v>5</v>
+      </c>
       <c r="U16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="s">
         <v>8</v>
@@ -1072,9 +1063,6 @@
         <v>8</v>
       </c>
       <c r="Z16" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1088,15 +1076,18 @@
       <c r="C17" t="s">
         <v>17</v>
       </c>
+      <c r="U17" t="s">
+        <v>5</v>
+      </c>
       <c r="V17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17" t="s">
-        <v>6</v>
-      </c>
-      <c r="X17" t="s">
         <v>19</v>
       </c>
+      <c r="Z17" t="s">
+        <v>8</v>
+      </c>
       <c r="AA17" t="s">
         <v>8</v>
       </c>
@@ -1104,9 +1095,6 @@
         <v>8</v>
       </c>
       <c r="AC17" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD17" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1120,19 +1108,19 @@
       <c r="C18" t="s">
         <v>18</v>
       </c>
+      <c r="V18" t="s">
+        <v>5</v>
+      </c>
       <c r="W18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1146,22 +1134,19 @@
       <c r="C19" t="s">
         <v>13</v>
       </c>
+      <c r="W19" t="s">
+        <v>5</v>
+      </c>
       <c r="X19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC19" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1175,19 +1160,19 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
+      <c r="X20" t="s">
+        <v>5</v>
+      </c>
       <c r="Y20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC20" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1201,22 +1186,19 @@
       <c r="C21" t="s">
         <v>21</v>
       </c>
+      <c r="Y21" t="s">
+        <v>5</v>
+      </c>
       <c r="Z21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1230,19 +1212,19 @@
       <c r="C22" t="s">
         <v>22</v>
       </c>
+      <c r="Z22" t="s">
+        <v>5</v>
+      </c>
       <c r="AA22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AD22" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE22" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1256,11 +1238,14 @@
       <c r="C23" t="s">
         <v>16</v>
       </c>
+      <c r="AA23" t="s">
+        <v>5</v>
+      </c>
       <c r="AB23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="s">
         <v>8</v>
@@ -1272,9 +1257,6 @@
         <v>8</v>
       </c>
       <c r="AG23" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH23" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1288,15 +1270,18 @@
       <c r="C24" t="s">
         <v>17</v>
       </c>
+      <c r="AB24" t="s">
+        <v>5</v>
+      </c>
       <c r="AC24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD24" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE24" t="s">
         <v>19</v>
       </c>
+      <c r="AG24" t="s">
+        <v>8</v>
+      </c>
       <c r="AH24" t="s">
         <v>8</v>
       </c>
@@ -1304,9 +1289,6 @@
         <v>8</v>
       </c>
       <c r="AJ24" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1320,19 +1302,19 @@
       <c r="C25" t="s">
         <v>18</v>
       </c>
+      <c r="AC25" t="s">
+        <v>5</v>
+      </c>
       <c r="AD25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK25" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ25" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1346,22 +1328,19 @@
       <c r="C26" t="s">
         <v>13</v>
       </c>
+      <c r="AD26" t="s">
+        <v>5</v>
+      </c>
       <c r="AE26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ26" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1375,19 +1354,19 @@
       <c r="C27" t="s">
         <v>20</v>
       </c>
+      <c r="AE27" t="s">
+        <v>5</v>
+      </c>
       <c r="AF27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH27" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK27" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ27" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1401,22 +1380,19 @@
       <c r="C28" t="s">
         <v>21</v>
       </c>
+      <c r="AF28" t="s">
+        <v>5</v>
+      </c>
       <c r="AG28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL28" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1430,19 +1406,19 @@
       <c r="C29" t="s">
         <v>22</v>
       </c>
+      <c r="AG29" t="s">
+        <v>5</v>
+      </c>
       <c r="AH29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1456,11 +1432,14 @@
       <c r="C30" t="s">
         <v>16</v>
       </c>
+      <c r="AH30" t="s">
+        <v>5</v>
+      </c>
       <c r="AI30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="s">
         <v>8</v>
@@ -1472,9 +1451,6 @@
         <v>8</v>
       </c>
       <c r="AN30" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO30" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1488,15 +1464,18 @@
       <c r="C31" t="s">
         <v>17</v>
       </c>
+      <c r="AI31" t="s">
+        <v>5</v>
+      </c>
       <c r="AJ31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL31" t="s">
         <v>19</v>
       </c>
+      <c r="AN31" t="s">
+        <v>8</v>
+      </c>
       <c r="AO31" t="s">
         <v>8</v>
       </c>
@@ -1504,9 +1483,6 @@
         <v>8</v>
       </c>
       <c r="AQ31" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR31" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1520,19 +1496,19 @@
       <c r="C32" t="s">
         <v>18</v>
       </c>
+      <c r="AJ32" t="s">
+        <v>5</v>
+      </c>
       <c r="AK32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM32" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ32" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1546,22 +1522,19 @@
       <c r="C33" t="s">
         <v>13</v>
       </c>
+      <c r="AK33" t="s">
+        <v>5</v>
+      </c>
       <c r="AL33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO33" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP33" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ33" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1575,19 +1548,19 @@
       <c r="C34" t="s">
         <v>20</v>
       </c>
+      <c r="AL34" t="s">
+        <v>5</v>
+      </c>
       <c r="AM34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN34" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO34" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR34" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ34" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1601,22 +1574,19 @@
       <c r="C35" t="s">
         <v>21</v>
       </c>
+      <c r="AM35" t="s">
+        <v>5</v>
+      </c>
       <c r="AN35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR35" t="s">
-        <v>10</v>
-      </c>
-      <c r="AS35" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1630,19 +1600,19 @@
       <c r="C36" t="s">
         <v>22</v>
       </c>
+      <c r="AN36" t="s">
+        <v>5</v>
+      </c>
       <c r="AO36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ36" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AR36" t="s">
-        <v>8</v>
-      </c>
-      <c r="AS36" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1656,11 +1626,14 @@
       <c r="C37" t="s">
         <v>16</v>
       </c>
+      <c r="AO37" t="s">
+        <v>5</v>
+      </c>
       <c r="AP37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ37" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR37" t="s">
         <v>8</v>
@@ -1672,9 +1645,6 @@
         <v>8</v>
       </c>
       <c r="AU37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV37" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1688,15 +1658,18 @@
       <c r="C38" t="s">
         <v>17</v>
       </c>
+      <c r="AP38" t="s">
+        <v>5</v>
+      </c>
       <c r="AQ38" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR38" t="s">
-        <v>6</v>
-      </c>
-      <c r="AS38" t="s">
         <v>19</v>
       </c>
+      <c r="AU38" t="s">
+        <v>8</v>
+      </c>
       <c r="AV38" t="s">
         <v>8</v>
       </c>
@@ -1704,9 +1677,6 @@
         <v>8</v>
       </c>
       <c r="AX38" t="s">
-        <v>8</v>
-      </c>
-      <c r="AY38" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1720,19 +1690,19 @@
       <c r="C39" t="s">
         <v>18</v>
       </c>
+      <c r="AQ39" t="s">
+        <v>5</v>
+      </c>
       <c r="AR39" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT39" t="s">
-        <v>8</v>
-      </c>
-      <c r="AU39" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY39" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX39" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1746,22 +1716,19 @@
       <c r="C40" t="s">
         <v>13</v>
       </c>
+      <c r="AR40" t="s">
+        <v>5</v>
+      </c>
       <c r="AS40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV40" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW40" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY40" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX40" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1775,19 +1742,19 @@
       <c r="C41" t="s">
         <v>20</v>
       </c>
+      <c r="AS41" t="s">
+        <v>5</v>
+      </c>
       <c r="AT41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU41" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV41" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW41" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY41" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1801,22 +1768,19 @@
       <c r="C42" t="s">
         <v>21</v>
       </c>
+      <c r="AT42" t="s">
+        <v>5</v>
+      </c>
       <c r="AU42" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV42" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AX42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AZ42" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1830,19 +1794,19 @@
       <c r="C43" t="s">
         <v>22</v>
       </c>
+      <c r="AU43" t="s">
+        <v>5</v>
+      </c>
       <c r="AV43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW43" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX43" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AY43" t="s">
-        <v>8</v>
-      </c>
-      <c r="AZ43" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1856,16 +1820,16 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
+      <c r="AX44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY44" t="s">
+        <v>6</v>
+      </c>
       <c r="AZ44" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA44" t="s">
-        <v>6</v>
-      </c>
-      <c r="BB44" t="s">
-        <v>8</v>
-      </c>
-      <c r="BC44" t="s">
         <v>11</v>
       </c>
     </row>
